--- a/model/data/invoice/buy/1405-06-19-buy-omid-worship-1789034294257.xlsx
+++ b/model/data/invoice/buy/1405-06-19-buy-omid-worship-1789034294257.xlsx
@@ -1,41 +1,409 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Dropbox\inventory-digi-2.7-1405\model\data\invoice\buy\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
+  <si>
+    <t>نام کالا</t>
+  </si>
+  <si>
+    <t>dkp</t>
+  </si>
+  <si>
+    <t>dkpc</t>
+  </si>
+  <si>
+    <t>کد هلو</t>
+  </si>
+  <si>
+    <t>تعداد</t>
+  </si>
+  <si>
+    <t>فی</t>
+  </si>
+  <si>
+    <t>کانتور مدادی ورشیپ مدل Master شماره 202</t>
+  </si>
+  <si>
+    <t>10673817</t>
+  </si>
+  <si>
+    <t>44092623</t>
+  </si>
+  <si>
+    <t>00216004</t>
+  </si>
+  <si>
+    <t>تینت لب ورشیپ مدل تینت شماره 301</t>
+  </si>
+  <si>
+    <t>9639270</t>
+  </si>
+  <si>
+    <t>34611707</t>
+  </si>
+  <si>
+    <t>00216005</t>
+  </si>
+  <si>
+    <t>تینت لب ورشیپ مدل تینت شماره 302</t>
+  </si>
+  <si>
+    <t>9639786</t>
+  </si>
+  <si>
+    <t>34611714</t>
+  </si>
+  <si>
+    <t>00216006</t>
+  </si>
+  <si>
+    <t>رژلب مایع ورشیپ مدل اکلیلی شاین شماره 102</t>
+  </si>
+  <si>
+    <t>15990759</t>
+  </si>
+  <si>
+    <t>55122207</t>
+  </si>
+  <si>
+    <t>00216024</t>
+  </si>
+  <si>
+    <t>رژلب مایع ورشیپ مدل اکلیلی شاین شماره 106</t>
+  </si>
+  <si>
+    <t>15991007</t>
+  </si>
+  <si>
+    <t>55122170</t>
+  </si>
+  <si>
+    <t>00216028</t>
+  </si>
+  <si>
+    <t>رژلب مایع ورشیپ مدل اکلیلی شاین شماره 107</t>
+  </si>
+  <si>
+    <t>15991066</t>
+  </si>
+  <si>
+    <t>55122165</t>
+  </si>
+  <si>
+    <t>00216029</t>
+  </si>
+  <si>
+    <t>رژگونه مایع مات ورشیپ مدل SMART CHEEK شماره C03</t>
+  </si>
+  <si>
+    <t>21976447</t>
+  </si>
+  <si>
+    <t>80158374</t>
+  </si>
+  <si>
+    <t>00216055</t>
+  </si>
+  <si>
+    <t>رژ لب مایع مخملی ورشیپ مدل VELVET شماره 220</t>
+  </si>
+  <si>
+    <t>22577679</t>
+  </si>
+  <si>
+    <t>83036824</t>
+  </si>
+  <si>
+    <t>00216057</t>
+  </si>
+  <si>
+    <t>رژ لب مایع مخملی ورشیپ مدل VELVET شماره 221</t>
+  </si>
+  <si>
+    <t>22577712</t>
+  </si>
+  <si>
+    <t>83036876</t>
+  </si>
+  <si>
+    <t>00216058</t>
+  </si>
+  <si>
+    <t>رژ لب مایع مخملی ورشیپ مدل MATTE شماره 222</t>
+  </si>
+  <si>
+    <t>22577754</t>
+  </si>
+  <si>
+    <t>83036872</t>
+  </si>
+  <si>
+    <t>00216059</t>
+  </si>
+  <si>
+    <t>رژ لب مایع مخملی ورشیپ مدل VELVET شماره 223</t>
+  </si>
+  <si>
+    <t>22577836</t>
+  </si>
+  <si>
+    <t>83036865</t>
+  </si>
+  <si>
+    <t>00216060</t>
+  </si>
+  <si>
+    <t>رژ لب مایع مخملی ورشیپ مدل VELVET شماره 224</t>
+  </si>
+  <si>
+    <t>22577851</t>
+  </si>
+  <si>
+    <t>83036855</t>
+  </si>
+  <si>
+    <t>00216061</t>
+  </si>
+  <si>
+    <t>رژ لب مایع مخملی ورشیپ مدل  VELVET شماره 225</t>
+  </si>
+  <si>
+    <t>22577866</t>
+  </si>
+  <si>
+    <t>83036851</t>
+  </si>
+  <si>
+    <t>00216062</t>
+  </si>
+  <si>
+    <t>رژ لب مایع مخملی ورشیپ مدل  VELVET MATTE شماره 226</t>
+  </si>
+  <si>
+    <t>22577924</t>
+  </si>
+  <si>
+    <t>83036845</t>
+  </si>
+  <si>
+    <t>00216063</t>
+  </si>
+  <si>
+    <t>رژ لب مایع مخملی ورشیپ مدل  VELVET MATTE شماره 227</t>
+  </si>
+  <si>
+    <t>22577937</t>
+  </si>
+  <si>
+    <t>83036841</t>
+  </si>
+  <si>
+    <t>00216064</t>
+  </si>
+  <si>
+    <t>رژ لب مایع مخملی ورشیپ مدل  VELVET MATTE شماره 228</t>
+  </si>
+  <si>
+    <t>22577956</t>
+  </si>
+  <si>
+    <t>83036838</t>
+  </si>
+  <si>
+    <t>00216065</t>
+  </si>
+  <si>
+    <t>رژ لب مایع مخملی ورشیپ مدل  VELVET MATTE شماره 229</t>
+  </si>
+  <si>
+    <t>22577988</t>
+  </si>
+  <si>
+    <t>83036834</t>
+  </si>
+  <si>
+    <t>00216066</t>
+  </si>
+  <si>
+    <t>رژ لب مایع مخملی ورشیپ مدل  VELVET MATTE شماره 230</t>
+  </si>
+  <si>
+    <t>22578007</t>
+  </si>
+  <si>
+    <t>83036829</t>
+  </si>
+  <si>
+    <t>00216067</t>
+  </si>
+  <si>
+    <t>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 101</t>
+  </si>
+  <si>
+    <t>22638040</t>
+  </si>
+  <si>
+    <t>83482444</t>
+  </si>
+  <si>
+    <t>00216068</t>
+  </si>
+  <si>
+    <t>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 102</t>
+  </si>
+  <si>
+    <t>22638070</t>
+  </si>
+  <si>
+    <t>83482459</t>
+  </si>
+  <si>
+    <t>00216069</t>
+  </si>
+  <si>
+    <t>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 103</t>
+  </si>
+  <si>
+    <t>22638104</t>
+  </si>
+  <si>
+    <t>83482621</t>
+  </si>
+  <si>
+    <t>00216070</t>
+  </si>
+  <si>
+    <t>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 104</t>
+  </si>
+  <si>
+    <t>22638124</t>
+  </si>
+  <si>
+    <t>83482599</t>
+  </si>
+  <si>
+    <t>00216071</t>
+  </si>
+  <si>
+    <t>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 105</t>
+  </si>
+  <si>
+    <t>22638146</t>
+  </si>
+  <si>
+    <t>83482581</t>
+  </si>
+  <si>
+    <t>00216072</t>
+  </si>
+  <si>
+    <t>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 106</t>
+  </si>
+  <si>
+    <t>22638160</t>
+  </si>
+  <si>
+    <t>83482558</t>
+  </si>
+  <si>
+    <t>00216073</t>
+  </si>
+  <si>
+    <t>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 107</t>
+  </si>
+  <si>
+    <t>22638178</t>
+  </si>
+  <si>
+    <t>83482528</t>
+  </si>
+  <si>
+    <t>00216074</t>
+  </si>
+  <si>
+    <t>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 108</t>
+  </si>
+  <si>
+    <t>22638204</t>
+  </si>
+  <si>
+    <t>83482497</t>
+  </si>
+  <si>
+    <t>00216075</t>
+  </si>
+  <si>
+    <t>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 109</t>
+  </si>
+  <si>
+    <t>22638224</t>
+  </si>
+  <si>
+    <t>83482680</t>
+  </si>
+  <si>
+    <t>00216076</t>
+  </si>
+  <si>
+    <t>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 110</t>
+  </si>
+  <si>
+    <t>22638238</t>
+  </si>
+  <si>
+    <t>83482690</t>
+  </si>
+  <si>
+    <t>00216077</t>
+  </si>
+  <si>
+    <t>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 111</t>
+  </si>
+  <si>
+    <t>22638258</t>
+  </si>
+  <si>
+    <t>83482718</t>
+  </si>
+  <si>
+    <t>00216078</t>
+  </si>
+  <si>
+    <t>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 112</t>
+  </si>
+  <si>
+    <t>22638274</t>
+  </si>
+  <si>
+    <t>83482753</t>
+  </si>
+  <si>
+    <t>00216079</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -72,6 +440,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,41 +772,42 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>نام کالا</v>
-      </c>
-      <c r="B1" t="str">
-        <v>dkp</v>
-      </c>
-      <c r="C1" t="str">
-        <v>dkpc</v>
-      </c>
-      <c r="D1" t="str">
-        <v>کد هلو</v>
-      </c>
-      <c r="E1" t="str">
-        <v>تعداد</v>
-      </c>
-      <c r="F1" t="str">
-        <v>فی</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>کانتور مدادی ورشیپ مدل Master شماره 202</v>
-      </c>
-      <c r="B2" t="str">
-        <v>10673817</v>
-      </c>
-      <c r="C2" t="str">
-        <v>44092623</v>
-      </c>
-      <c r="D2" t="str">
-        <v>00216004</v>
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
       </c>
       <c r="E2">
         <v>80</v>
@@ -439,58 +816,58 @@
         <v>1800000</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>تینت لب ورشیپ مدل تینت شماره 301</v>
-      </c>
-      <c r="B3" t="str">
-        <v>9639270</v>
-      </c>
-      <c r="C3" t="str">
-        <v>34611707</v>
-      </c>
-      <c r="D3" t="str">
-        <v>00216005</v>
+    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
       </c>
       <c r="E3">
         <v>9</v>
       </c>
       <c r="F3">
-        <v>1080000</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>تینت لب ورشیپ مدل تینت شماره 302</v>
-      </c>
-      <c r="B4" t="str">
-        <v>9639786</v>
-      </c>
-      <c r="C4" t="str">
-        <v>34611714</v>
-      </c>
-      <c r="D4" t="str">
-        <v>00216006</v>
+        <v>1800000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
       </c>
       <c r="E4">
         <v>24</v>
       </c>
       <c r="F4">
-        <v>1080000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>رژلب مایع ورشیپ مدل اکلیلی شاین شماره 102</v>
-      </c>
-      <c r="B5" t="str">
-        <v>15990759</v>
-      </c>
-      <c r="C5" t="str">
-        <v>55122207</v>
-      </c>
-      <c r="D5" t="str">
-        <v>00216024</v>
+        <v>1800000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
       </c>
       <c r="E5">
         <v>36</v>
@@ -499,18 +876,18 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>رژلب مایع ورشیپ مدل اکلیلی شاین شماره 106</v>
-      </c>
-      <c r="B6" t="str">
-        <v>15991007</v>
-      </c>
-      <c r="C6" t="str">
-        <v>55122170</v>
-      </c>
-      <c r="D6" t="str">
-        <v>00216028</v>
+    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
       </c>
       <c r="E6">
         <v>36</v>
@@ -519,18 +896,18 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>رژلب مایع ورشیپ مدل اکلیلی شاین شماره 107</v>
-      </c>
-      <c r="B7" t="str">
-        <v>15991066</v>
-      </c>
-      <c r="C7" t="str">
-        <v>55122165</v>
-      </c>
-      <c r="D7" t="str">
-        <v>00216029</v>
+    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>29</v>
       </c>
       <c r="E7">
         <v>24</v>
@@ -539,18 +916,18 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>رژگونه مایع مات ورشیپ مدل SMART CHEEK شماره C03</v>
-      </c>
-      <c r="B8" t="str">
-        <v>21976447</v>
-      </c>
-      <c r="C8" t="str">
-        <v>80158374</v>
-      </c>
-      <c r="D8" t="str">
-        <v>00216055</v>
+    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>33</v>
       </c>
       <c r="E8">
         <v>12</v>
@@ -559,18 +936,18 @@
         <v>3680000</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>رژ لب مایع مخملی ورشیپ مدل VELVET شماره 220</v>
-      </c>
-      <c r="B9" t="str">
-        <v>22577679</v>
-      </c>
-      <c r="C9" t="str">
-        <v>83036824</v>
-      </c>
-      <c r="D9" t="str">
-        <v>00216057</v>
+    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>37</v>
       </c>
       <c r="E9">
         <v>6</v>
@@ -579,18 +956,18 @@
         <v>2800000</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>رژ لب مایع مخملی ورشیپ مدل VELVET شماره 221</v>
-      </c>
-      <c r="B10" t="str">
-        <v>22577712</v>
-      </c>
-      <c r="C10" t="str">
-        <v>83036876</v>
-      </c>
-      <c r="D10" t="str">
-        <v>00216058</v>
+    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" t="s">
+        <v>41</v>
       </c>
       <c r="E10">
         <v>6</v>
@@ -599,18 +976,18 @@
         <v>2800000</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>رژ لب مایع مخملی ورشیپ مدل MATTE شماره 222</v>
-      </c>
-      <c r="B11" t="str">
-        <v>22577754</v>
-      </c>
-      <c r="C11" t="str">
-        <v>83036872</v>
-      </c>
-      <c r="D11" t="str">
-        <v>00216059</v>
+    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" t="s">
+        <v>45</v>
       </c>
       <c r="E11">
         <v>6</v>
@@ -619,18 +996,18 @@
         <v>2800000</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>رژ لب مایع مخملی ورشیپ مدل VELVET شماره 223</v>
-      </c>
-      <c r="B12" t="str">
-        <v>22577836</v>
-      </c>
-      <c r="C12" t="str">
-        <v>83036865</v>
-      </c>
-      <c r="D12" t="str">
-        <v>00216060</v>
+    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" t="s">
+        <v>49</v>
       </c>
       <c r="E12">
         <v>6</v>
@@ -639,18 +1016,18 @@
         <v>2800000</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>رژ لب مایع مخملی ورشیپ مدل VELVET شماره 224</v>
-      </c>
-      <c r="B13" t="str">
-        <v>22577851</v>
-      </c>
-      <c r="C13" t="str">
-        <v>83036855</v>
-      </c>
-      <c r="D13" t="str">
-        <v>00216061</v>
+    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" t="s">
+        <v>53</v>
       </c>
       <c r="E13">
         <v>6</v>
@@ -659,18 +1036,18 @@
         <v>2800000</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>رژ لب مایع مخملی ورشیپ مدل  VELVET شماره 225</v>
-      </c>
-      <c r="B14" t="str">
-        <v>22577866</v>
-      </c>
-      <c r="C14" t="str">
-        <v>83036851</v>
-      </c>
-      <c r="D14" t="str">
-        <v>00216062</v>
+    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" t="s">
+        <v>57</v>
       </c>
       <c r="E14">
         <v>6</v>
@@ -679,18 +1056,18 @@
         <v>2800000</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>رژ لب مایع مخملی ورشیپ مدل  VELVET MATTE شماره 226</v>
-      </c>
-      <c r="B15" t="str">
-        <v>22577924</v>
-      </c>
-      <c r="C15" t="str">
-        <v>83036845</v>
-      </c>
-      <c r="D15" t="str">
-        <v>00216063</v>
+    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" t="s">
+        <v>61</v>
       </c>
       <c r="E15">
         <v>6</v>
@@ -699,18 +1076,18 @@
         <v>2800000</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>رژ لب مایع مخملی ورشیپ مدل  VELVET MATTE شماره 227</v>
-      </c>
-      <c r="B16" t="str">
-        <v>22577937</v>
-      </c>
-      <c r="C16" t="str">
-        <v>83036841</v>
-      </c>
-      <c r="D16" t="str">
-        <v>00216064</v>
+    <row r="16" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" t="s">
+        <v>65</v>
       </c>
       <c r="E16">
         <v>6</v>
@@ -719,18 +1096,18 @@
         <v>2800000</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>رژ لب مایع مخملی ورشیپ مدل  VELVET MATTE شماره 228</v>
-      </c>
-      <c r="B17" t="str">
-        <v>22577956</v>
-      </c>
-      <c r="C17" t="str">
-        <v>83036838</v>
-      </c>
-      <c r="D17" t="str">
-        <v>00216065</v>
+    <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
       </c>
       <c r="E17">
         <v>6</v>
@@ -739,18 +1116,18 @@
         <v>2800000</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>رژ لب مایع مخملی ورشیپ مدل  VELVET MATTE شماره 229</v>
-      </c>
-      <c r="B18" t="str">
-        <v>22577988</v>
-      </c>
-      <c r="C18" t="str">
-        <v>83036834</v>
-      </c>
-      <c r="D18" t="str">
-        <v>00216066</v>
+    <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" t="s">
+        <v>73</v>
       </c>
       <c r="E18">
         <v>6</v>
@@ -759,18 +1136,18 @@
         <v>2800000</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>رژ لب مایع مخملی ورشیپ مدل  VELVET MATTE شماره 230</v>
-      </c>
-      <c r="B19" t="str">
-        <v>22578007</v>
-      </c>
-      <c r="C19" t="str">
-        <v>83036829</v>
-      </c>
-      <c r="D19" t="str">
-        <v>00216067</v>
+    <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" t="s">
+        <v>77</v>
       </c>
       <c r="E19">
         <v>6</v>
@@ -779,18 +1156,18 @@
         <v>2800000</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 101</v>
-      </c>
-      <c r="B20" t="str">
-        <v>22638040</v>
-      </c>
-      <c r="C20" t="str">
-        <v>83482444</v>
-      </c>
-      <c r="D20" t="str">
-        <v>00216068</v>
+    <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" t="s">
+        <v>81</v>
       </c>
       <c r="E20">
         <v>12</v>
@@ -799,18 +1176,18 @@
         <v>2320000</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 102</v>
-      </c>
-      <c r="B21" t="str">
-        <v>22638070</v>
-      </c>
-      <c r="C21" t="str">
-        <v>83482459</v>
-      </c>
-      <c r="D21" t="str">
-        <v>00216069</v>
+    <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" t="s">
+        <v>85</v>
       </c>
       <c r="E21">
         <v>12</v>
@@ -819,18 +1196,18 @@
         <v>2320000</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 103</v>
-      </c>
-      <c r="B22" t="str">
-        <v>22638104</v>
-      </c>
-      <c r="C22" t="str">
-        <v>83482621</v>
-      </c>
-      <c r="D22" t="str">
-        <v>00216070</v>
+    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" t="s">
+        <v>89</v>
       </c>
       <c r="E22">
         <v>12</v>
@@ -839,18 +1216,18 @@
         <v>2320000</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 104</v>
-      </c>
-      <c r="B23" t="str">
-        <v>22638124</v>
-      </c>
-      <c r="C23" t="str">
-        <v>83482599</v>
-      </c>
-      <c r="D23" t="str">
-        <v>00216071</v>
+    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" t="s">
+        <v>93</v>
       </c>
       <c r="E23">
         <v>12</v>
@@ -859,18 +1236,18 @@
         <v>2320000</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 105</v>
-      </c>
-      <c r="B24" t="str">
-        <v>22638146</v>
-      </c>
-      <c r="C24" t="str">
-        <v>83482581</v>
-      </c>
-      <c r="D24" t="str">
-        <v>00216072</v>
+    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" t="s">
+        <v>97</v>
       </c>
       <c r="E24">
         <v>12</v>
@@ -879,18 +1256,18 @@
         <v>2320000</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 106</v>
-      </c>
-      <c r="B25" t="str">
-        <v>22638160</v>
-      </c>
-      <c r="C25" t="str">
-        <v>83482558</v>
-      </c>
-      <c r="D25" t="str">
-        <v>00216073</v>
+    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" t="s">
+        <v>101</v>
       </c>
       <c r="E25">
         <v>12</v>
@@ -899,18 +1276,18 @@
         <v>2320000</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 107</v>
-      </c>
-      <c r="B26" t="str">
-        <v>22638178</v>
-      </c>
-      <c r="C26" t="str">
-        <v>83482528</v>
-      </c>
-      <c r="D26" t="str">
-        <v>00216074</v>
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" t="s">
+        <v>104</v>
+      </c>
+      <c r="D26" t="s">
+        <v>105</v>
       </c>
       <c r="E26">
         <v>12</v>
@@ -919,18 +1296,18 @@
         <v>2320000</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 108</v>
-      </c>
-      <c r="B27" t="str">
-        <v>22638204</v>
-      </c>
-      <c r="C27" t="str">
-        <v>83482497</v>
-      </c>
-      <c r="D27" t="str">
-        <v>00216075</v>
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>106</v>
+      </c>
+      <c r="B27" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" t="s">
+        <v>108</v>
+      </c>
+      <c r="D27" t="s">
+        <v>109</v>
       </c>
       <c r="E27">
         <v>12</v>
@@ -939,18 +1316,18 @@
         <v>2320000</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 109</v>
-      </c>
-      <c r="B28" t="str">
-        <v>22638224</v>
-      </c>
-      <c r="C28" t="str">
-        <v>83482680</v>
-      </c>
-      <c r="D28" t="str">
-        <v>00216076</v>
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" t="s">
+        <v>113</v>
       </c>
       <c r="E28">
         <v>12</v>
@@ -959,18 +1336,18 @@
         <v>2320000</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 110</v>
-      </c>
-      <c r="B29" t="str">
-        <v>22638238</v>
-      </c>
-      <c r="C29" t="str">
-        <v>83482690</v>
-      </c>
-      <c r="D29" t="str">
-        <v>00216077</v>
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" t="s">
+        <v>117</v>
       </c>
       <c r="E29">
         <v>12</v>
@@ -979,18 +1356,18 @@
         <v>2320000</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 111</v>
-      </c>
-      <c r="B30" t="str">
-        <v>22638258</v>
-      </c>
-      <c r="C30" t="str">
-        <v>83482718</v>
-      </c>
-      <c r="D30" t="str">
-        <v>00216078</v>
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>118</v>
+      </c>
+      <c r="B30" t="s">
+        <v>119</v>
+      </c>
+      <c r="C30" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" t="s">
+        <v>121</v>
       </c>
       <c r="E30">
         <v>12</v>
@@ -999,18 +1376,18 @@
         <v>2320000</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 112</v>
-      </c>
-      <c r="B31" t="str">
-        <v>22638274</v>
-      </c>
-      <c r="C31" t="str">
-        <v>83482753</v>
-      </c>
-      <c r="D31" t="str">
-        <v>00216079</v>
+    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>122</v>
+      </c>
+      <c r="B31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" t="s">
+        <v>124</v>
+      </c>
+      <c r="D31" t="s">
+        <v>125</v>
       </c>
       <c r="E31">
         <v>12</v>
@@ -1020,8 +1397,9 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F31"/>
+    <ignoredError sqref="A1:F2 A5:F31 A3:E3 A4:E4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>